--- a/tabular/legacy/dbm-gifford-legacy-list-hg19.xlsx
+++ b/tabular/legacy/dbm-gifford-legacy-list-hg19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robgifford/Repo/erv/locus/ERVdb-HomoSapiens/tabular/legacy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A23584-E6F0-574A-B8F0-EB458F69A100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6097EFB8-C720-0344-8FE4-62A263C1576B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="940" windowWidth="28040" windowHeight="17180" xr2:uid="{16BBA012-6A39-5942-9F82-0CAD6162F56D}"/>
   </bookViews>
@@ -2321,6 +2321,7 @@
   <dimension ref="A1:O142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="4" max="4" width="40.6640625" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="18.5" customWidth="1"/>
